--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/8182-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/8182-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0FD58689-4338-46D5-A524-D32CF7644BF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D67B1B7B-1A9F-4A7E-A834-0ECCD23EB020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{4D121395-FD56-454F-80AE-F1231FB5B2C5}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{3CA57507-F87D-4626-9083-0F182C9AC56C}"/>
   </bookViews>
   <sheets>
     <sheet name="8182-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1451,25 +1451,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5A19292-F6DD-45CD-9A45-23D24EF083A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F2FC535-096C-444D-9968-2FA2F5ABCC47}">
   <dimension ref="A1:R36"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1497,7 +1497,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1527,7 +1527,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1623,7 +1623,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2025</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="40">
         <v>2024</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>3.22</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="38">
         <v>2023</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>3.26</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="40">
         <v>2022</v>
       </c>
@@ -1839,7 +1839,7 @@
         <v>7.76</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
         <v>25</v>
       </c>
@@ -1895,7 +1895,7 @@
         <v>7.76</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>25</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="38">
         <v>2021</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>2.87</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2117,7 +2117,7 @@
         <v>2.87</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="40">
         <v>2020</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>3.29</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
         <v>25</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>25</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>3.29</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="38">
         <v>2019</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>5.08</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="40">
         <v>2018</v>
       </c>
@@ -2391,7 +2391,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="38">
         <v>2017</v>
       </c>
@@ -2445,7 +2445,7 @@
         <v>4.2300000000000004</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="40">
         <v>2016</v>
       </c>
@@ -2499,7 +2499,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="38">
         <v>2015</v>
       </c>
@@ -2553,7 +2553,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="40">
         <v>2014</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>3.17</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="38">
         <v>2013</v>
       </c>
@@ -2661,7 +2661,7 @@
         <v>2.31</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="40">
         <v>2012</v>
       </c>
@@ -2715,7 +2715,7 @@
         <v>5.74</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="38">
         <v>2011</v>
       </c>
@@ -2769,7 +2769,7 @@
         <v>5.88</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="40">
         <v>2010</v>
       </c>
@@ -2823,7 +2823,7 @@
         <v>3.39</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="38">
         <v>2009</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>3.61</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="40">
         <v>2008</v>
       </c>
@@ -2931,7 +2931,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="38">
         <v>2007</v>
       </c>
@@ -2985,7 +2985,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="40">
         <v>2006</v>
       </c>
@@ -3039,7 +3039,7 @@
         <v>4.3899999999999997</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="38">
         <v>2005</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>5.59</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="40">
         <v>2004</v>
       </c>
@@ -3147,7 +3147,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="38">
         <v>2002</v>
       </c>
@@ -3201,7 +3201,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="40">
         <v>2001</v>
       </c>
@@ -3255,7 +3255,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="38">
         <v>2000</v>
       </c>
@@ -3309,7 +3309,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="40" t="s">
         <v>35</v>
       </c>
